--- a/Result/checksun_type/運動用品.xlsx
+++ b/Result/checksun_type/運動用品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>71.84</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>72.81</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>71.2</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>71.2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6007.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3975.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3975.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5226.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>9884.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>9884.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1007.629459538829</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6007</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6007.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>71.52</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>72.88</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>71.08</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>71.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3105.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3817.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3817.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5350.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>9990.72</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>9990.719999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1202.131223237939</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3105</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3105.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>71.26</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.95999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6515.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4568.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>4568.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6809.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>10092.02</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>10092.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1126.129056263883</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6515</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6515.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>71.14</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>70.84</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>70.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2752.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>5094.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>5094.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6660.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>10198.06</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>10198.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1342.692780005807</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2752</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2752.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>71.3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>70.76</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>70.76000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1497.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5808.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5808</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>7118.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>10467.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>10467.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1200.937643208348</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1497</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1497.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>71.64000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>72.89</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>70.67</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70.67</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>5219.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6478.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6478</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8354.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>10724.64</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>10724.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-821.0753890973956</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>5219</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>5219.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>72.18</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>72.82</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>70.58</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>70.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6861.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6884.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6884</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>9685.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>11306.28</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>11306.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-647.8766193282718</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6861</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6861.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>72.94</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>72.76</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>70.43</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>72.76000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70.43000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9142.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>9050.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>9050.200000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>10481.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11334.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11334.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-553.2399261106566</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9142</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9142.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>73.06</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>72.68</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>70.25</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>6321.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>8225.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>8225.799999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>10498.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11308.92</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11308.92</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-642.6789384386811</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>6321</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>6321.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>73.24</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>72.61</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>70.08</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>70.08</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>4847.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8429.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>8429.200000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>10884.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12040.9</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12040.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-445.246136820193</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>4847</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>4847.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>73.32000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>72.51</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>69.85</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>69.84999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>7249.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>10230.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>10230.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>11336.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>12307.36</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>12307.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>10.63094180694316</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>7249</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7249.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>17.17</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18.36</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>5213.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3408.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3408.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>4264.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>45001.12</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>45001.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1644.892935262787</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>5213</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>5213.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>16.98</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18.36</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2261.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3191.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3191.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>4582.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>45105.76</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>45105.76</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1964.001474831271</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2261</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2261.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>16.96</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>18.37</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2719.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3726.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3726.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>5032.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>45605.5</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>45605.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2033.442192970843</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2719</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2719.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>17.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>17.68</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>18.39</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3773.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>4395.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>4395.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>6412.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>45661.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>45661.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2109.091711992703</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3773</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3773.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>17.38</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>17.77</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>18.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3075.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>4131.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>4131.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>6330.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>45684.02</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>45684.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-2254.766320881335</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3075</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3075.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>17.54</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>18.44</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>4128.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>5119.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>5119.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>6523.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>45983.48</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>45983.48</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-2307.559822119332</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>4128</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>4128.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>17.75</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>17.92</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>18.45</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>4936.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>5973.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>5973</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>7256.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>45992.26</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>45992.26</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2413.387687383638</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>4936</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>4936.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>17.82</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>18.47</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>18.47</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>6066.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>6339.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>6339.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>7445.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>46024.48</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>46024.48</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2564.949363211804</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>6066</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>6066.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>18.47</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>18.47</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2453.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>8430.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>8430</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>7612.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>46106.82</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>46106.82</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-2810.932137137333</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2453</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2453.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>17.71</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>17.96</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>18.48</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>18.48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>8016.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8529.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>8529.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>7907.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>46246.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>46246.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2674.838523561755</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>8016</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>8016.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>17.67</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>18.49</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8394.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>7927.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>7927.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>7706.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>46325.06</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>46325.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-2980.924842612296</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8394</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8394.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>18.83</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>134</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>113.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>150.4</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>5.094059701290561</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>275</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18.87</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>152.68</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>152.68</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-9.995558126169087</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>19</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>17.61</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>128.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>152.7</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3.766599375176838</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>18</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>18.93</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>129.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>129.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>109.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>153.1</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>5.373577389639848</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>231</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>18.95</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>104.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>149.36</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-4.582369281680613</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>127</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>147.2</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-7.498637052078394</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>72</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>18.51</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>19.01</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>147.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>147.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-5.504068257929575</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>196</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,21 +13527,17 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AM31" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO31" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP31" t="inlineStr">
         <is>
           <t>12.53</t>
@@ -13756,20 +13578,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>145.88</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-15.74382468564805</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>22</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,21 +13957,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AM32" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO32" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP32" t="inlineStr">
         <is>
           <t>21.95</t>
@@ -14192,20 +14008,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>89.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>105.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>149.38</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>149.38</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-11.1669115579013</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>146</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>96.59999999999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>109.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>148.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>148.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-17.51536024833804</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>26</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>18.66</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>103.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>149.84</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>149.84</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-13.10188122580702</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>26</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>17.5</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>17.27</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>648.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>747.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>747.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1142.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1113.16</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1113.16</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-37.38959462215303</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>648</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>648.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17.24</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>940.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1114.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1114.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1187.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1110.56</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1110.56</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-12.61855469609031</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>940</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>940.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>17.48</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>17.22</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>357.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1018.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1018</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1149.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1111.18</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1111.18</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-8.066406419711825</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>357</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>357.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>17.43</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>17.19</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17.19</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>762.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1269.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1269.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1212.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>1128.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>1128.94</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>61.18903420439005</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>762</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>762.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.16</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1029.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1602.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1602.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1206.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1124.06</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1124.06</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>114.5471981600929</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1029</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1029.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>17.46</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>17.36</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2486.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1537.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1537.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1149.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1131.66</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1131.66</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>158.0750324482367</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2486</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2486.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1259.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1259.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>977.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1094.82</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1094.82</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>58.50497312957646</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>456</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>17.49</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.08</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1613.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1281.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1281.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>967.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1126.14</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1126.14</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>131.67256791972</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1613</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1613.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>17.48</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.05</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2427.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1155.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1155</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>884.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1099.34</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1099.34</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>107.5308259085064</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2427</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2427.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>17.42</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>705.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>811.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>811.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>768.2</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1060.42</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1060.42</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-18.01204931853101</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>705</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>705.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>17.35</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>17.31</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1097.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>761.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>761.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>781.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1065.34</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1065.34</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-12.21572645292258</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1097</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1097.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>20.39</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3111603.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>7746104.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>7746104.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9050560.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>10123667.06</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>10123667.06</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-771459.655962158</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3111603</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3111603.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>7571166.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>8563180.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>8563180.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>11611277.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>10267424.2</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>10267424.2</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-297801.5701538436</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>7571166</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>7571166.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>16673233.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>8717070.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>8717070.199999999</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>11266208.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>10273960.5</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>10273960.5</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-88321.71292218566</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>16673233</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>16673233.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>20.28</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>7787838.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>7789054.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>7789054.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>10120826.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>10049815.34</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>10049815.34</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-761131.8914154526</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>7787838</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>7787838.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>20.47</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>3586684.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>8268244.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>8268244</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>10538446.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>10010900.14</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>10010900.14</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-743099.4002838545</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>3586684</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>3586684.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>20.66</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>7196981.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>10355016.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>10355016.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>11515321.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>10079136.34</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>10079136.34</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-240675.7915142905</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>7196981</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>7196981.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>20.85</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>8340615.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>14659375.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>14659375.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>11858116.5</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>10161117.42</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>10161117.42</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>98850.2492820248</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>8340615</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>8340615.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>20.89</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>12033153.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>13815347.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>13815347.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>12611250.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>10116463.34</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>10116463.34</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>457824.8700881209</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>12033153</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>12033153.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>20.88</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>10183787.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>12452599.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>12452599.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>12062049.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>10008415.46</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>10008415.46</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>558665.79730797</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>10183787</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>10183787.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>20.73</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>14020546.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>12808648.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>12808648.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>11848845.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>10016520.52</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>10016520.52</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>880918.2720038947</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>14020546</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>14020546.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>20.59</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>28718775.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>12675626.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>12675626</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>10947329.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>10085969.44</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>10085969.44</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>898736.261855077</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>28718775</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>28718775.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
